--- a/artfynd/A 12146-2025 artfynd.xlsx
+++ b/artfynd/A 12146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116527871</v>
+        <v>116528273</v>
       </c>
       <c r="B2" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576572</v>
+        <v>576550</v>
       </c>
       <c r="R2" t="n">
-        <v>7059575</v>
+        <v>7059597</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116525018</v>
+        <v>117990306</v>
       </c>
       <c r="B3" t="n">
-        <v>82338</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576582</v>
+        <v>576656</v>
       </c>
       <c r="R3" t="n">
-        <v>7059672</v>
+        <v>7059523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116523880</v>
+        <v>116525018</v>
       </c>
       <c r="B4" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576540</v>
+        <v>576582</v>
       </c>
       <c r="R4" t="n">
-        <v>7059700</v>
+        <v>7059672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116527686</v>
+        <v>116527791</v>
       </c>
       <c r="B5" t="n">
-        <v>90460</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576582</v>
+        <v>576552</v>
       </c>
       <c r="R5" t="n">
-        <v>7059572</v>
+        <v>7059577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116528273</v>
+        <v>117988507</v>
       </c>
       <c r="B6" t="n">
-        <v>90438</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Rörmyrbäcken, Rörmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576550</v>
+        <v>576616</v>
       </c>
       <c r="R6" t="n">
-        <v>7059597</v>
+        <v>7059770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,67 +1198,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116528105</v>
+        <v>117989020</v>
       </c>
       <c r="B7" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Rörmyrbäcken, Rörmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576569</v>
+        <v>576689</v>
       </c>
       <c r="R7" t="n">
-        <v>7059567</v>
+        <v>7059716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,67 +1305,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116527570</v>
+        <v>122246455</v>
       </c>
       <c r="B8" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Rörmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576589</v>
+        <v>576688</v>
       </c>
       <c r="R8" t="n">
-        <v>7059578</v>
+        <v>7059716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,24 +1380,19 @@
           <t>Ramsele</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Y-Sol-0092</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:39</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:39</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1407,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1470,54 +1415,53 @@
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116525974</v>
+        <v>116523880</v>
       </c>
       <c r="B9" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576572</v>
+        <v>576540</v>
       </c>
       <c r="R9" t="n">
-        <v>7059682</v>
+        <v>7059700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1493,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1503,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,55 +1530,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116527326</v>
+        <v>117990623</v>
       </c>
       <c r="B10" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576637</v>
+        <v>576483</v>
       </c>
       <c r="R10" t="n">
-        <v>7059562</v>
+        <v>7059658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,22 +1595,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,67 +1625,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116528020</v>
+        <v>123188319</v>
       </c>
       <c r="B11" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576562</v>
+        <v>576512</v>
       </c>
       <c r="R11" t="n">
-        <v>7059575</v>
+        <v>7059717</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,22 +1702,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,62 +1732,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116527791</v>
+        <v>123188706</v>
       </c>
       <c r="B12" t="n">
-        <v>82338</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576552</v>
+        <v>576451</v>
       </c>
       <c r="R12" t="n">
-        <v>7059577</v>
+        <v>7059679</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,22 +1809,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,55 +1851,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116528129</v>
+        <v>116525974</v>
       </c>
       <c r="B13" t="n">
-        <v>56490</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576566</v>
+        <v>576572</v>
       </c>
       <c r="R13" t="n">
-        <v>7059564</v>
+        <v>7059682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +1921,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +1931,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,12 +1946,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2052,12 +1961,7 @@
         <v>116527100</v>
       </c>
       <c r="B14" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,7 +1994,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2166,15 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117990062</v>
+        <v>116527326</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,14 +2106,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576725</v>
+        <v>576637</v>
       </c>
       <c r="R15" t="n">
-        <v>7059574</v>
+        <v>7059562</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,22 +2140,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,27 +2170,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117990623</v>
+        <v>116527570</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,34 +2193,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576483</v>
+        <v>576589</v>
       </c>
       <c r="R16" t="n">
-        <v>7059658</v>
+        <v>7059578</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,22 +2252,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,15 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117989928</v>
+        <v>116527871</v>
       </c>
       <c r="B17" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,43 +2305,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sågbäcken (Sågbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576763</v>
+        <v>576572</v>
       </c>
       <c r="R17" t="n">
-        <v>7059587</v>
+        <v>7059575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,22 +2364,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,15 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117989314</v>
+        <v>116528020</v>
       </c>
       <c r="B18" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,42 +2417,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576747</v>
+        <v>576562</v>
       </c>
       <c r="R18" t="n">
-        <v>7059647</v>
+        <v>7059575</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,22 +2476,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,27 +2506,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117990000</v>
+        <v>116528105</v>
       </c>
       <c r="B19" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,14 +2554,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576723</v>
+        <v>576569</v>
       </c>
       <c r="R19" t="n">
-        <v>7059563</v>
+        <v>7059567</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,22 +2588,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,27 +2618,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117990252</v>
+        <v>117990000</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2791,14 +2666,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576710</v>
+        <v>576723</v>
       </c>
       <c r="R20" t="n">
-        <v>7059531</v>
+        <v>7059563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2715,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,15 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117990357</v>
+        <v>117990062</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,14 +2778,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576621</v>
+        <v>576725</v>
       </c>
       <c r="R21" t="n">
-        <v>7059500</v>
+        <v>7059574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2817,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2827,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,15 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117990520</v>
+        <v>117990252</v>
       </c>
       <c r="B22" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,34 +2865,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576525</v>
+        <v>576710</v>
       </c>
       <c r="R22" t="n">
-        <v>7059628</v>
+        <v>7059531</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +2929,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +2939,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,15 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117990306</v>
+        <v>117990357</v>
       </c>
       <c r="B23" t="n">
-        <v>90500</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,34 +2977,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576656</v>
+        <v>576621</v>
       </c>
       <c r="R23" t="n">
-        <v>7059523</v>
+        <v>7059500</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,15 +3078,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117989020</v>
+        <v>116528129</v>
       </c>
       <c r="B24" t="n">
-        <v>100080</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,34 +3089,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rörmyrbäcken (Rörmyrbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576689</v>
+        <v>576566</v>
       </c>
       <c r="R24" t="n">
-        <v>7059716</v>
+        <v>7059564</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,22 +3148,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3308,65 +3178,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122246455</v>
+        <v>117989314</v>
       </c>
       <c r="B25" t="n">
-        <v>100594</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rörmyrbäcken, Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576688</v>
+        <v>576747</v>
       </c>
       <c r="R25" t="n">
-        <v>7059716</v>
+        <v>7059647</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,19 +3258,24 @@
           <t>Ramsele</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Y-Sol-0092</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,7 +3290,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3423,11 +3298,123 @@
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117989928</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sågbäcken, Sågbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>576763</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7059587</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12146-2025 artfynd.xlsx
+++ b/artfynd/A 12146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990306</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116525018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527791</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117988507</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117989020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116523880</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990623</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188319</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188706</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116525974</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527326</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527570</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527871</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528020</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2627,6 +2717,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528105</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2739,6 +2834,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990000</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2851,6 +2951,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990062</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2963,6 +3068,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990252</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3075,6 +3185,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990357</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3187,6 +3302,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528129</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3299,6 +3419,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117989314</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3415,8 +3540,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117989928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>